--- a/Tools/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Tools/Luban/DataTables/Datas/__tables__.xlsx
@@ -1,20 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13120"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="tables" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -31,91 +44,79 @@
     <t>input</t>
   </si>
   <si>
+    <t>index</t>
+  </si>
+  <si>
     <t>mode</t>
   </si>
   <si>
-    <t>index</t>
-  </si>
-  <si>
     <t>group</t>
   </si>
   <si>
     <t>comment</t>
   </si>
   <si>
+    <t>tags</t>
+  </si>
+  <si>
     <t>output</t>
   </si>
   <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>TbMachine</t>
-  </si>
-  <si>
-    <t>Machine</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>machine.xlsx</t>
-  </si>
-  <si>
-    <t>map</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>机器配置表</t>
-  </si>
-  <si>
-    <t>TbRecipe</t>
-  </si>
-  <si>
-    <t>Recipe</t>
-  </si>
-  <si>
-    <t>recipe.xlsx</t>
-  </si>
-  <si>
-    <t>配方配置表</t>
-  </si>
-  <si>
-    <t>TbResource</t>
-  </si>
-  <si>
-    <t>Resource</t>
-  </si>
-  <si>
-    <t>resource.xlsx</t>
-  </si>
-  <si>
-    <t>资源配置表</t>
-  </si>
-  <si>
-    <t>TbMilestone</t>
-  </si>
-  <si>
-    <t>Milestone</t>
-  </si>
-  <si>
-    <t>milestone.xlsx</t>
-  </si>
-  <si>
-    <t>里程碑配置表</t>
-  </si>
-  <si>
-    <t>TbTilePrice</t>
-  </si>
-  <si>
-    <t>TilePrice</t>
-  </si>
-  <si>
-    <t>tileprice.xlsx</t>
-  </si>
-  <si>
-    <t>地块价格表</t>
+    <t>##</t>
+  </si>
+  <si>
+    <t>全名(包含模块和名字)</t>
+  </si>
+  <si>
+    <t>记录类名</t>
+  </si>
+  <si>
+    <t>从excel读取定义</t>
+  </si>
+  <si>
+    <t>文件列表</t>
+  </si>
+  <si>
+    <t>表id字段</t>
+  </si>
+  <si>
+    <t>模式</t>
+  </si>
+  <si>
+    <t>分组</t>
+  </si>
+  <si>
+    <t>注释</t>
+  </si>
+  <si>
+    <t>输出文件名</t>
+  </si>
+  <si>
+    <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
+  </si>
+  <si>
+    <t>可以多个，以逗号','分隔</t>
+  </si>
+  <si>
+    <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
+  </si>
+  <si>
+    <t>取值one|map|list，为空自动为map</t>
+  </si>
+  <si>
+    <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
+  </si>
+  <si>
+    <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>TbLanguage</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
+    <t>Language.xlsx</t>
   </si>
   <si>
     <t>TbUIWindow</t>
@@ -124,25 +125,7 @@
     <t>UIWindow</t>
   </si>
   <si>
-    <t>uiwindow.xlsx</t>
-  </si>
-  <si>
-    <t>UI窗口配置表</t>
-  </si>
-  <si>
-    <t>TbLanguage</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>language.xlsx</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>多语言表</t>
+    <t>UIWindow.xlsx</t>
   </si>
   <si>
     <t>TbTime</t>
@@ -157,7 +140,13 @@
     <t>one</t>
   </si>
   <si>
-    <t>时间表</t>
+    <t>TbReputation</t>
+  </si>
+  <si>
+    <t>Reputation</t>
+  </si>
+  <si>
+    <t>名声_Reputation.xlsx</t>
   </si>
 </sst>
 </file>
@@ -170,18 +159,18 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="宋体"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -189,7 +178,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -197,14 +186,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -212,7 +201,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -220,7 +209,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -228,7 +217,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -236,7 +225,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -244,14 +233,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -259,7 +248,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -267,7 +256,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -275,14 +264,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -290,47 +279,40 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -339,8 +321,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -369,12 +351,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -530,27 +506,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -653,155 +614,164 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -854,7 +824,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -864,7 +834,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -874,44 +844,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -938,14 +908,15 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -972,6 +943,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -983,160 +955,131 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1148,22 +1091,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="8" customWidth="1"/>
+    <col min="1" max="1" width="9" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="31.25" style="2" customWidth="1"/>
+    <col min="6" max="9" width="18" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1198,192 +1138,123 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="2:9">
-      <c r="B2" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:11">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="3" spans="2:9">
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="4" spans="2:9">
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" t="s">
-        <v>25</v>
+    <row r="4" spans="1:11">
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" t="s">
-        <v>29</v>
+    <row r="5" spans="1:11">
+      <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="6" spans="2:9">
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" t="s">
+    <row r="6" spans="1:11">
+      <c r="B6" s="2" t="s">
         <v>33</v>
       </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="7" spans="2:9">
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" t="s">
+    <row r="7" spans="1:11">
+      <c r="B7" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="2:9">
-      <c r="B8" t="s">
+      <c r="C7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" spans="2:9">
-      <c r="B9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Tools/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Tools/Luban/DataTables/Datas/__tables__.xlsx
@@ -1,320 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>value_type</t>
-  </si>
-  <si>
-    <t>read_schema_from_file</t>
-  </si>
-  <si>
-    <t>input</t>
-  </si>
-  <si>
-    <t>index</t>
-  </si>
-  <si>
-    <t>mode</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>output</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>记录类名</t>
-  </si>
-  <si>
-    <t>从excel读取定义</t>
-  </si>
-  <si>
-    <t>文件列表</t>
-  </si>
-  <si>
-    <t>表id字段</t>
-  </si>
-  <si>
-    <t>模式</t>
-  </si>
-  <si>
-    <t>分组</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>输出文件名</t>
-  </si>
-  <si>
-    <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
-  </si>
-  <si>
-    <t>可以多个，以逗号','分隔</t>
-  </si>
-  <si>
-    <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
-  </si>
-  <si>
-    <t>取值one|map|list，为空自动为map</t>
-  </si>
-  <si>
-    <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
-  </si>
-  <si>
-    <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>TbLanguage</t>
-  </si>
-  <si>
-    <t>Language</t>
-  </si>
-  <si>
-    <t>Language.xlsx</t>
-  </si>
-  <si>
-    <t>TbUIWindow</t>
-  </si>
-  <si>
-    <t>UIWindow</t>
-  </si>
-  <si>
-    <t>UIWindow.xlsx</t>
-  </si>
-  <si>
-    <t>TbTime</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>时间_Time.xlsx</t>
-  </si>
-  <si>
-    <t>one</t>
-  </si>
-  <si>
-    <t>TbReputation</t>
-  </si>
-  <si>
-    <t>Reputation</t>
-  </si>
-  <si>
-    <t>名声_Reputation.xlsx</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -614,164 +471,165 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -825,11 +683,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1089,172 +1010,360 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="9" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32.375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="31.25" style="2" customWidth="1"/>
-    <col min="6" max="9" width="18" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2" customWidth="1"/>
+    <col width="9" customWidth="1" style="2" min="1" max="1"/>
+    <col width="33" customWidth="1" style="2" min="2" max="2"/>
+    <col width="19" customWidth="1" style="2" min="3" max="3"/>
+    <col width="40" customWidth="1" style="2" min="4" max="4"/>
+    <col width="37" customWidth="1" style="2" min="5" max="5"/>
+    <col width="40" customWidth="1" style="2" min="6" max="9"/>
+    <col width="40" customWidth="1" style="3" min="7" max="7"/>
+    <col width="40" customWidth="1" style="3" min="8" max="8"/>
+    <col width="25" customWidth="1" style="3" min="9" max="9"/>
+    <col width="8" customWidth="1" style="2" min="10" max="16384"/>
+    <col width="38" customWidth="1" style="3" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
+    <row r="1" customFormat="1" s="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>value_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>read_schema_from_file</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>index</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
+    <row r="2" customFormat="1" s="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>记录类名</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>从excel读取定义</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>文件列表</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>表id字段</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>模式</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>输出文件名</t>
+        </is>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>26</v>
+    <row r="3" customFormat="1" s="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>可以多个，以逗号','分隔</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>取值one|map|list，为空自动为map</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="B4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>28</v>
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>TbLanguage</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
       </c>
       <c r="D4" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Language.xlsx</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="B5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>31</v>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>TbUIWindow</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>UIWindow</t>
+        </is>
       </c>
       <c r="D5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>32</v>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>UIWindow.xlsx</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="B6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>34</v>
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>TbTime</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
       </c>
       <c r="D6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>36</v>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>时间_Time.xlsx</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="B7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>38</v>
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>TbReputation</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Reputation</t>
+        </is>
       </c>
       <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>39</v>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>名声_Reputation.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>TbHerb</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Herb</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>药材_Herb.xlsx</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>药材配置表</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>TbCause</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Cause</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>病因_Cause.xlsx</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>病因配置表</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>TbSymptom</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Symptom</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>病症_Symptom.xlsx</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>病症配置表</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>TbVisitorTemplate</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>VisitorTemplate</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>来客_VisitorTemplate.xlsx</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>来客模板配置表</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Tools/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Tools/Luban/DataTables/Datas/__tables__.xlsx
@@ -430,14 +430,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
@@ -522,7 +522,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>item.xlsx</t>
+          <t>物品_Item.xlsx</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>crop.xlsx</t>
+          <t>作物_Crop.xlsx</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>tree.xlsx</t>
+          <t>树木_Tree.xlsx</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>animal.xlsx</t>
+          <t>动物_Animal.xlsx</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>building.xlsx</t>
+          <t>建筑_Building.xlsx</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>recipe.xlsx</t>
+          <t>配方_Recipe.xlsx</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>visitor.xlsx</t>
+          <t>来客_Visitor.xlsx</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>order.xlsx</t>
+          <t>订单_Order.xlsx</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>milestone.xlsx</t>
+          <t>里程碑_Milestone.xlsx</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>season.xlsx</t>
+          <t>季节_Season.xlsx</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>time.xlsx</t>
+          <t>时间_Time.xlsx</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>expansion.xlsx</t>
+          <t>扩建_Expansion.xlsx</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>obstacle.xlsx</t>
+          <t>障碍物_Obstacle.xlsx</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>shop.xlsx</t>
+          <t>商店_Shop.xlsx</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>uiwindow.xlsx</t>
+          <t>UI窗口_UIWindow.xlsx</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>language.xlsx</t>
+          <t>多语言_Language.xlsx</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>weather.xlsx</t>
+          <t>天气_Weather.xlsx</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1199,6 +1199,43 @@
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TbStartingResource</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>StartingResource</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>初始资源_StartingResource.xlsx</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>初始资源表</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Tools/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Tools/Luban/DataTables/Datas/__tables__.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="tables" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tables" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
@@ -1237,6 +1237,43 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TbGameConfig</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>GameConfig</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>游戏配置_GameConfig.xlsx</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>全局游戏配置表</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
